--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_242_Fiji.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_242_Fiji.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb1414bdce3fb4346"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb0607328d8134d9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Refad44b923f44621"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R3e2ca5582acf4ed5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9c92be4aa5eb4bab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R31ea59e752194e6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R05ce4804ff77451f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rc6d8875332b544e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf2bbb7e00086454b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rae2662eddf734791"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rbfe2bb1c36a344c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R9f8e39ad777f4979"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ242CommercialTable" displayName="EEZ242CommercialTable" ref="A1:O8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O8"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ242CommercialTable" displayName="EEZ242CommercialTable" ref="A1:E8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E8"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ242FunctionalTable" displayName="EEZ242FunctionalTable" ref="A1:O14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O14"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ242FunctionalTable" displayName="EEZ242FunctionalTable" ref="A1:E14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E14"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ242ValidationTable" displayName="EEZ242ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ242ValidationTable" displayName="EEZ242ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4513,7 +4467,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3b247ccf3c14f5b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0ce0b4fc2404971"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4523,20 +4477,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4544,444 +4488,155 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>520.677135663</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.7369710876116895</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>54.572152943467024</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>520.677135663</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>61.03744296933625</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$58,A2,'Species'!$U$2:$U$58))</x:f>
-        <x:v>31780.80097346771</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.7369710876116895</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>54.572152943467024</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>28414.472281567563</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>3366.3286919001475</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1184723284156814</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.11847232841568137</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>16</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.57</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>371.5352290971724</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$58,A3,'Species'!$U$2:$U$58))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>5944.563665554759</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.57</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>5944.563665554759</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2848.9592518299996</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.390652048720636</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>24.58397177998317</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>2848.9592518299996</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>35.918653312570754</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$58,A4,'Species'!$U$2:$U$58))</x:f>
-        <x:v>102330.7796681227</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.390652048720636</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>24.58397177998317</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>70038.73384931068</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>32292.045818812025</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.4610598171047582</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.4610598171047583</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>7979.208446803001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.9749485068571953</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>94.3948948131822</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>7979.208446803001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>137.3149597394016</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$58,A5,'Species'!$U$2:$U$58))</x:f>
-        <x:v>1095664.6866250471</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.9749485068571953</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>94.3948948131822</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>753196.5420284242</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>342468.1445966229</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.4546862943294008</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.45468629432940066</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>19177.329477338502</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.5118990393606837</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>325.0117329744605</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>19177.329477338502</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>807.690054944518</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$58,A6,'Species'!$U$2:$U$58))</x:f>
-        <x:v>15489338.29924066</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.5118990393606837</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>325.0117329744605</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>6232857.087251991</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>9256481.211988669</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>2.485110452944745</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>1.485110452944745</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>11712.812678226099</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.359237761471045</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2286.850433634409</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>11712.812678226099</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2321.824855814035</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$58,A7,'Species'!$U$2:$U$58))</x:f>
-        <x:v>27195099.607799113</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.359237761471045</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2286.850433634409</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>26785450.752279956</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>409648.8555191569</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.015293707741106</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.015293707741105979</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>15306.8407589031</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.358577963517813</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2283.3787946471757</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>15306.8407589031</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2318.7591925845404</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$58,A8,'Species'!$U$2:$U$58))</x:f>
-        <x:v>35492877.719134286</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.358577963517813</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2283.3787946471757</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>34951315.60192042</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>541562.1172138676</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0154947562884904</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.015494756288490358</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G8">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O8">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bcd6f0470c642a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6648815cdfb445ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4991,20 +4646,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5012,768 +4657,269 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>92</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.58</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>380.1893963205613</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>380.1893963205613</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$58,A2,'Species'!$U$2:$U$58))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>34977.42446149164</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.58</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>380.1893963205613</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>34977.42446149164</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>32.999999996</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.03</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>10.71519305237606</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>32.999999996</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>10.71519305237606</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$58,A3,'Species'!$U$2:$U$58))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>353.6013706855492</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.03</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>10.71519305237606</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>353.6013706855492</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>17467.415801143703</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.361105574504147</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2296.7068965642347</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>17467.415801143703</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2331.6367082340985</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$58,A4,'Species'!$U$2:$U$58))</x:f>
-        <x:v>40727667.87993498</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.361105574504147</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2296.7068965642347</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>40117534.33564183</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>610133.5442931503</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.015208650142566</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.01520865014256587</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>11712.812678226099</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.359237761471045</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2286.850433634409</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>11712.812678226099</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2321.824855814035</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$58,A5,'Species'!$U$2:$U$58))</x:f>
-        <x:v>27195099.607799113</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.359237761471045</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2286.850433634409</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>26785450.752279956</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>409648.8555191569</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.015293707741106</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.015293707741105979</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>235</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.7819148936170213</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>60.52222609402345</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>74.31075591539367</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$58,A6,'Species'!$U$2:$U$58))</x:f>
-        <x:v>17463.027640117514</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.7819148936170213</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>60.52222609402345</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>14222.72313209551</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>3240.3045080220036</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.2278258866412026</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.22782588664120274</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2452.3761837306</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.28</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>190.54607179632464</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2452.3761837306</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$58,A7,'Species'!$U$2:$U$58))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>467290.64837672753</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.28</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>467290.64837672753</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>4254.0836353643</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.039288397142614</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1094.6830590572702</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>4254.0836353643</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1355.1531436487242</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$58,A8,'Species'!$U$2:$U$58))</x:f>
-        <x:v>5764934.811808524</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.039288397142614</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1094.6830590572702</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>4656873.287446064</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1108061.5243624598</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2379410939416275</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.23794109394162755</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>13681.602010213997</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.2738816930296273</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>187.88049383257396</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>13681.602010213997</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>354.1539971471843</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$58,A9,'Species'!$U$2:$U$58))</x:f>
-        <x:v>4845394.039294239</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.2738816930296273</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>187.88049383257396</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2570506.1420997423</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2274887.897194497</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.8849960947131732</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.8849960947131731</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5726.239593134</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.4065918439740765</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>25.503033652719665</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5726.239593134</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>31.25043128893368</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$58,A10,'Species'!$U$2:$U$58))</x:f>
-        <x:v>178947.4569492056</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.4065918439740765</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>25.503033652719665</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>146036.48104723217</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>32910.975901973434</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.2253613320861185</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.22536133208611847</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>285.677135663</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>50.11872336272725</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>285.677135663</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>50.11872336272725</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$58,A11,'Species'!$U$2:$U$58))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>14317.7733333502</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>50.11872336272725</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>14317.7733333502</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>114.999999994</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.2308695652187414</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>170.16473636653583</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>114.999999994</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>170.88320668618422</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$58,A12,'Species'!$U$2:$U$58))</x:f>
-        <x:v>19651.56876788589</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.2308695652187414</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>170.16473636653583</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>19568.944681130633</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>82.62408675525512</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.004222204523626</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.004222204523625919</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>16</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.57</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>371.5352290971724</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$58,A13,'Species'!$U$2:$U$58))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>5944.563665554759</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.57</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>5944.563665554759</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1490.6207112979998</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.595181632264115</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>39.37147018646277</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1490.6207112979998</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>94.58747797861534</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$58,A14,'Species'!$U$2:$U$58))</x:f>
-        <x:v>140994.05370436748</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.595181632264115</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>39.37147018646277</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>58687.92889419313</x:v>
       </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>82306.12481017435</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.4024370319586814</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.4024370319586814</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G14">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O14">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd482a0d3f3a04717"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9600f19f1304ce1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5948,7 +5094,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6047,7 +5193,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>79413036.45710625</x:v>
+        <x:v>68827217.75327721</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6061,7 +5207,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>79413036.45710625</x:v>
+        <x:v>74891764.60643005</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6075,7 +5221,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-10585818.703829035</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6089,7 +5235,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-4521271.850676194</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6100,9 +5246,9 @@
         <x:v>EEZ_242</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6114,47 +5260,19 @@
         <x:v>EEZ_242</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_242</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_242</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa6fe2abcf044b23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb8c37e6fd034d9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6201,7 +5319,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
